--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA219"/>
+  <dimension ref="A1:AA220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23172,6 +23172,95 @@
         </is>
       </c>
     </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>50А bulevard</t>
+        </is>
+      </c>
+      <c r="H220" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="J220" s="2" t="inlineStr"/>
+      <c r="K220" s="2" t="inlineStr"/>
+      <c r="L220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr"/>
+      <c r="N220" s="2" t="inlineStr">
+        <is>
+          <t>asen.tsekov@vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="O220" s="2" t="inlineStr"/>
+      <c r="P220" s="2" t="inlineStr"/>
+      <c r="Q220" s="2" t="inlineStr"/>
+      <c r="R220" s="2" t="inlineStr"/>
+      <c r="S220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinoorendawineshop/</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoorenda</t>
+        </is>
+      </c>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="2" t="inlineStr"/>
+      <c r="W220" s="2" t="inlineStr">
+        <is>
+          <t>Asen Tsekov</t>
+        </is>
+      </c>
+      <c r="X220" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y220" s="2" t="inlineStr"/>
+      <c r="Z220" s="2" t="inlineStr"/>
+      <c r="AA220" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asen-tsekov-27a47555/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA220"/>
+  <dimension ref="A1:AA223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23261,6 +23261,289 @@
         </is>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Avanti 777 Eood</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>Avanti 777 Eood</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>62571</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>120 Bulevard</t>
+        </is>
+      </c>
+      <c r="H221" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>https://avanti-bg.com</t>
+        </is>
+      </c>
+      <c r="J221" s="2" t="inlineStr"/>
+      <c r="K221" s="2" t="inlineStr"/>
+      <c r="L221" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="M221" s="2" t="inlineStr"/>
+      <c r="N221" s="2" t="inlineStr">
+        <is>
+          <t>avanti2006@abv.bg</t>
+        </is>
+      </c>
+      <c r="O221" s="2" t="inlineStr"/>
+      <c r="P221" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q221" s="2" t="inlineStr">
+        <is>
+          <t>105568755</t>
+        </is>
+      </c>
+      <c r="R221" s="2" t="inlineStr"/>
+      <c r="S221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/magaziniavanti/</t>
+        </is>
+      </c>
+      <c r="T221" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/magazini_avanti/</t>
+        </is>
+      </c>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="2" t="inlineStr"/>
+      <c r="W221" s="2" t="inlineStr"/>
+      <c r="X221" s="2" t="inlineStr"/>
+      <c r="Y221" s="2" t="inlineStr"/>
+      <c r="Z221" s="2" t="inlineStr"/>
+      <c r="AA221" s="2" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Sid Commercial Ood</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Sid Commercial Ood</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>25032</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>247 Boulevard</t>
+        </is>
+      </c>
+      <c r="H222" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sid-shop.com</t>
+        </is>
+      </c>
+      <c r="J222" s="2" t="inlineStr"/>
+      <c r="K222" s="2" t="inlineStr"/>
+      <c r="L222" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M222" s="2" t="inlineStr"/>
+      <c r="N222" s="2" t="inlineStr">
+        <is>
+          <t>sid-shop@sidcommercial.com</t>
+        </is>
+      </c>
+      <c r="O222" s="2" t="inlineStr"/>
+      <c r="P222" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q222" s="2" t="inlineStr">
+        <is>
+          <t>831591274</t>
+        </is>
+      </c>
+      <c r="R222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/s-&amp;-d-commercial-ltd./</t>
+        </is>
+      </c>
+      <c r="S222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sid.commercial/</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sidcommercial/</t>
+        </is>
+      </c>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="2" t="inlineStr"/>
+      <c r="W222" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Atanasov</t>
+        </is>
+      </c>
+      <c r="X222" s="2" t="inlineStr">
+        <is>
+          <t>Online Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y222" s="2" t="inlineStr"/>
+      <c r="Z222" s="2" t="inlineStr"/>
+      <c r="AA222" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kirilatanasov</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>50А bulevard</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr"/>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>asen.tsekov@vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr"/>
+      <c r="P223" s="2" t="inlineStr"/>
+      <c r="Q223" s="2" t="inlineStr"/>
+      <c r="R223" s="2" t="inlineStr"/>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinoorendawineshop/</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoorenda</t>
+        </is>
+      </c>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>Asen Tsekov</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asen-tsekov-27a47555/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Bulgaria.xlsx
+++ b/BWI/bestwine_output/bestwine_Bulgaria.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA223"/>
+  <dimension ref="A1:AA232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -23544,6 +23544,899 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Vayk Wines Ead</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Vayk Wines Ead</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>7 Iskarsko Shose Blvd.</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://vaykwines.com</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr"/>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>info@vaykwines.com</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr"/>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>175086039</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr"/>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinello.Bulgaria/</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>Kristiana Boyadzhieva</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Vayk Wines Ead</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Vayk Wines Ead</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>7 Iskarsko Shose Blvd.</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>1528</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://vaykwines.com</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr"/>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>info@vaykwines.com</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr"/>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>175086039</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr"/>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Vinello.Bulgaria/</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr">
+        <is>
+          <t>Georgi Apostolov</t>
+        </is>
+      </c>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>47995</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>106 Bulevard Bulgaria</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://seewines.com</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr"/>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>info@seewines.com</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>205017678</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seewines/</t>
+        </is>
+      </c>
+      <c r="S226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Seewines</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seewines</t>
+        </is>
+      </c>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCjVgL7IXXbWL-ViDQHTwtaw?</t>
+        </is>
+      </c>
+      <c r="W226" s="2" t="inlineStr">
+        <is>
+          <t>Dilyana Vasileva</t>
+        </is>
+      </c>
+      <c r="X226" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dilyanavasileva/</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>47995</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>106 Bulevard Bulgaria</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://seewines.com</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr"/>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>info@seewines.com</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr"/>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>205017678</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seewines/</t>
+        </is>
+      </c>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Seewines</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seewines</t>
+        </is>
+      </c>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCjVgL7IXXbWL-ViDQHTwtaw?</t>
+        </is>
+      </c>
+      <c r="W227" s="2" t="inlineStr">
+        <is>
+          <t>Nadya Toteva</t>
+        </is>
+      </c>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>Business Manager</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nadya-toteva-53959651/</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>Seewines Logistics Eood</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>47995</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>106 Bulevard Bulgaria</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://seewines.com</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr"/>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>info@seewines.com</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>205017678</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seewines/</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Seewines</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/seewines</t>
+        </is>
+      </c>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCjVgL7IXXbWL-ViDQHTwtaw?</t>
+        </is>
+      </c>
+      <c r="W228" s="2" t="inlineStr">
+        <is>
+          <t>Evgeni Yordanov</t>
+        </is>
+      </c>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Specialist</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/evgeni-yordanov-09113777/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Proftrade Eood</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>Proftrade Eood</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>21367</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>8 Srebrostruy Str.</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>1373</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.proftrade.org</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr"/>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>office@proftrade-bg.com</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>130782782</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr"/>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/proftradeood/</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr"/>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>Zornitsa Todorova</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr">
+        <is>
+          <t>https://bg.linkedin.com/in/zornitsa-todorova-9351494b</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Avanti 777 Eood</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Avanti 777 Eood</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>62571</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>120 Bulevard</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://avanti-bg.com</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr"/>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>avanti2006@abv.bg</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>105568755</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr"/>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/magaziniavanti/</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/magazini_avanti/</t>
+        </is>
+      </c>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr"/>
+      <c r="X230" s="2" t="inlineStr"/>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Sid Commercial Ood</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Sid Commercial Ood</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>25032</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>247 Boulevard</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>1839</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sid-shop.com</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr"/>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>sid-shop@sidcommercial.com</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr"/>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>831591274</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/s-&amp;-d-commercial-ltd./</t>
+        </is>
+      </c>
+      <c r="S231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/sid.commercial/</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sidcommercial/</t>
+        </is>
+      </c>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr">
+        <is>
+          <t>Kiril Atanasov</t>
+        </is>
+      </c>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>Online Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kirilatanasov</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>Vino Orenda</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Sofia</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Sofia-City</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>50А bulevard</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>1606</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr"/>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>asen.tsekov@vinoorenda.com</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr"/>
+      <c r="P232" s="2" t="inlineStr"/>
+      <c r="Q232" s="2" t="inlineStr"/>
+      <c r="R232" s="2" t="inlineStr"/>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/vinoorendawineshop/</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinoorenda</t>
+        </is>
+      </c>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr">
+        <is>
+          <t>Asen Tsekov</t>
+        </is>
+      </c>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/asen-tsekov-27a47555/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
